--- a/Pacifico_Bambu_Financial_Model_v2.xlsx
+++ b/Pacifico_Bambu_Financial_Model_v2.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capex" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earn-Loss &amp; Dividends" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earn-Loss" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +77,16 @@
       <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +108,18 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -119,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,6 +165,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -614,21 +641,21 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Bridge Funding (MXN)</t>
+          <t>Bridge Round (MXN, 2026)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Major Funding (MXN)</t>
+          <t>Seed Round (MXN, 2028)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +695,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15">
@@ -688,7 +715,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -850,7 +877,7 @@
         <v>2027</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C34" s="9">
         <f>C33+B34</f>
@@ -862,7 +889,7 @@
         <v>2028</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C35" s="9">
         <f>C34+B35</f>
@@ -874,7 +901,7 @@
         <v>2029</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C36" s="9">
         <f>C35+B36</f>
@@ -898,7 +925,7 @@
         <v>2031</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C38" s="9">
         <f>C37+B38</f>
@@ -910,7 +937,7 @@
         <v>2032</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C39" s="9">
         <f>C38+B39</f>
@@ -922,7 +949,11 @@
         <v>2033</v>
       </c>
       <c r="B40" s="20" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <f>C39+B40</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -981,24 +1012,24 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Treatment Pools - Small (10 × 30 poles)</t>
+          <t>Truck (main vehicle)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>1300000</v>
+        <v>1500000</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>2026</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Drying Yard</t>
+          <t>Small Bodega (10ha, drying)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>15000</v>
+        <v>130000</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>2026</v>
@@ -1007,14 +1038,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Warehouse Phase 1 (Azulillo)</t>
+          <t>Warehouse Expansion (Azulillo)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
         <v>130000</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="49">
@@ -1027,7 +1058,7 @@
         <v>130000</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>2029</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="50">
@@ -1040,59 +1071,59 @@
         <v>120000</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Platform + Warehouse Expansion</t>
+          <t>Pickup #1</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>80000</v>
+        <v>750000</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>2028</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Road Improvements</t>
+          <t>Road Improvements (for scale)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
         <v>500000</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>2026</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Vehicles (Truck + 2 Pickups)</t>
+          <t>Pickup #2</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>3000000</v>
+        <v>750000</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>2027</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Nursery Infrastructure</t>
+          <t>Nursery Infrastructure (basic)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="55">
@@ -1105,140 +1136,1316 @@
         <v>500000</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>2029</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ICC-ES Certification</t>
+          <t>ICC-ES Certification (1yr before full maturity)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
         <v>2500000</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>2031</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>Big Bodega (near road)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>TOTAL CAPEX</t>
         </is>
       </c>
-      <c r="B57" s="10">
-        <f>SUM(B44:B55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58"/>
+      <c r="B58">
+        <f>SUM(B45:B57)</f>
+        <v/>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>TREATMENT POOL PARAMETERS</t>
-        </is>
-      </c>
+      <c r="A59" s="1" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>Small Pool: Poles per batch</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="A60" s="18" t="n"/>
+      <c r="B60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>Small Pool: Days per batch</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n">
+      <c r="A61" s="18" t="n"/>
+      <c r="B61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="n"/>
+      <c r="B62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="n"/>
+      <c r="B63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="n"/>
+      <c r="B64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="n"/>
+      <c r="B65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="n"/>
+      <c r="B66" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="n"/>
+      <c r="B68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="n"/>
+      <c r="B69" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="inlineStr">
+        <is>
+          <t>WORKFORCE MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="23" t="inlineStr">
+        <is>
+          <t>Workers per team</t>
+        </is>
+      </c>
+      <c r="B74" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>Internal team size</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>Working days/year</t>
+        </is>
+      </c>
+      <c r="B75" s="23">
+        <f>B16*12</f>
+        <v/>
+      </c>
+      <c r="C75" s="23" t="inlineStr">
+        <is>
+          <t>6 days × 52 weeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>Annual cost per team (MXN)</t>
+        </is>
+      </c>
+      <c r="B76" s="23">
+        <f>B74*B14*B16*12</f>
+        <v/>
+      </c>
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>2 × 450 × 26 × 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>Hectares per maintenance team</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>1 team handles 25 ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t>Establishment time per ha (days)</t>
+        </is>
+      </c>
+      <c r="B78" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="C78" s="23" t="inlineStr">
+        <is>
+          <t>After external clearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="inlineStr">
+        <is>
+          <t>EXTERNAL CLEARING (CONTRACTOR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>Cost per ha cleared (MXN)</t>
+        </is>
+      </c>
+      <c r="B82" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>Outsourced for new land prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="inlineStr">
+        <is>
+          <t>Time saved per ha (days)</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>4 weeks of clearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>PER-HECTARE MATERIALS (one-time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>Water pipes/ha (MXN)</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>Pipes for irrigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>Path materials/ha (MXN)</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C88" s="23" t="inlineStr">
+        <is>
+          <t>Light tractor + paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t>Total materials/ha</t>
+        </is>
+      </c>
+      <c r="B89" s="23">
+        <f>B87+B88</f>
+        <v/>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>Excludes seedlings</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>PROCESSING INFRASTRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="inlineStr">
+        <is>
+          <t>Pool capacity (poles/batch)</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>Simultaneous capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="23" t="inlineStr">
+        <is>
+          <t>Pool batch days</t>
+        </is>
+      </c>
+      <c r="B94" s="23" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>Small Pool: Count</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>Small Pool: Cost each (MXN)</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
+      <c r="C94" s="23" t="inlineStr">
+        <is>
+          <t>Soaking time</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="inlineStr">
+        <is>
+          <t>Pool capacity/year</t>
+        </is>
+      </c>
+      <c r="B95" s="23">
+        <f>B93*FLOOR(365/B94,1)</f>
+        <v/>
+      </c>
+      <c r="C95" s="23" t="inlineStr">
+        <is>
+          <t>~2,400 poles/year/pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="23" t="inlineStr">
+        <is>
+          <t>Pool cost (MXN)</t>
+        </is>
+      </c>
+      <c r="B96" s="23" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C96" s="23" t="inlineStr">
+        <is>
+          <t>1.8m × 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="23" t="inlineStr">
+        <is>
+          <t>Pool liquids/year (MXN)</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C97" s="23" t="inlineStr">
+        <is>
+          <t>Annual chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="23" t="inlineStr">
+        <is>
+          <t>Pools needed per 10 ha (mature)</t>
+        </is>
+      </c>
+      <c r="B98" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" s="23" t="inlineStr">
+        <is>
+          <t>For 10,000 poles/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t>BODEGAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="23" t="inlineStr">
+        <is>
+          <t>Small bodega (per 10 ha)</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="n">
         <v>130000</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="18" t="inlineStr">
-        <is>
-          <t>Large Pool: Poles per batch</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="18" t="inlineStr">
-        <is>
-          <t>Large Pool: Days per treatment</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
+      <c r="C102" s="23" t="inlineStr">
+        <is>
+          <t>Capacity 1,000 poles/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="23" t="inlineStr">
+        <is>
+          <t>Big bodega (near road)</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
+        <is>
+          <t>Central warehouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="23" t="inlineStr">
+        <is>
+          <t>Big bodega year</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="n">
+        <v>2034</v>
+      </c>
+      <c r="C104" s="23" t="inlineStr">
+        <is>
+          <t>When scale demands it</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="inlineStr">
+        <is>
+          <t>SG&amp;A &amp; OVERHEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="23" t="inlineStr">
+        <is>
+          <t>SG&amp;A 2026 base (MXN)</t>
+        </is>
+      </c>
+      <c r="B108" s="23" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C108" s="23" t="inlineStr">
+        <is>
+          <t>Minimal: phone, basic legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="23" t="inlineStr">
+        <is>
+          <t>SG&amp;A 2027 (MXN)</t>
+        </is>
+      </c>
+      <c r="B109" s="23" t="n">
+        <v>75000</v>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>Slight growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="23" t="inlineStr">
+        <is>
+          <t>SG&amp;A 2028 (MXN)</t>
+        </is>
+      </c>
+      <c r="B110" s="23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>Add accountant</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="23" t="inlineStr">
+        <is>
+          <t>SG&amp;A growth from 2029 (%)</t>
+        </is>
+      </c>
+      <c r="B111" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>Per year after</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="23" t="inlineStr">
+        <is>
+          <t>Mgmt start year</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C112" s="23" t="inlineStr">
+        <is>
+          <t>No mgmt salary 2026-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="23" t="inlineStr">
+        <is>
+          <t>Mgmt monthly (MXN)</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>Per manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="23" t="inlineStr">
+        <is>
+          <t>Number of managers</t>
+        </is>
+      </c>
+      <c r="B114" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
+        <is>
+          <t>Diego, Juan, Ofir</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
+        <is>
+          <t>NURSERY &amp; CONSULTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B117" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="23" t="inlineStr">
+        <is>
+          <t>Nursery labor/year (MXN)</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>No nursery costs until 2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="23" t="inlineStr">
+        <is>
+          <t>Nursery start year</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>External seedlings until then</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="23" t="inlineStr">
+        <is>
+          <t>Consulting/year (MXN)</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C120" s="23" t="inlineStr">
+        <is>
+          <t>Light advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t>Consulting start year</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>When complexity grows</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="23" t="inlineStr">
+        <is>
+          <t>Carbon verification/year</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C122" s="23" t="inlineStr">
+        <is>
+          <t>Verra process</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="23" t="inlineStr">
+        <is>
+          <t>Carbon verification start</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>After plantation matures</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>TRACTOR &amp; LOGISTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C126" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>Tractor cost/ha/year (MXN)</t>
+        </is>
+      </c>
+      <c r="B127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="23" t="inlineStr">
+        <is>
+          <t>Workers do paths manually now</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="23" t="inlineStr">
+        <is>
+          <t>Tractor start year</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C128" s="23" t="inlineStr">
+        <is>
+          <t>Only at scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="23" t="inlineStr">
+        <is>
+          <t>Logistics cost per pole (MXN)</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" s="23" t="inlineStr">
+        <is>
+          <t>Transport to buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="21" t="inlineStr">
+        <is>
+          <t>BASE 10HA PRODUCTION (SURVEY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B132" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C132" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="23" t="inlineStr">
+        <is>
+          <t>Existing surviving plants</t>
+        </is>
+      </c>
+      <c r="B133" s="23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C133" s="23" t="inlineStr">
+        <is>
+          <t>Survey: 1,500 healthy plants on 10 ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="23" t="inlineStr">
+        <is>
+          <t>Target plants per ha</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="C134" s="23" t="inlineStr">
+        <is>
+          <t>After densification</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="23" t="inlineStr">
+        <is>
+          <t>2026 production</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C135" s="23" t="inlineStr">
+        <is>
+          <t>Survey: max sellable</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="23" t="inlineStr">
+        <is>
+          <t>2027 production</t>
+        </is>
+      </c>
+      <c r="B136" s="23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>Survey: real estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="23" t="inlineStr">
+        <is>
+          <t>2028 production</t>
+        </is>
+      </c>
+      <c r="B137" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C137" s="23" t="inlineStr">
+        <is>
+          <t>1,000 plants reach maturity (yr5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="23" t="inlineStr">
+        <is>
+          <t>2029 production</t>
+        </is>
+      </c>
+      <c r="B138" s="23" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>1,000 yr6 (2/plant) + 500 yr5 (1/plant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="23" t="inlineStr">
+        <is>
+          <t>2030 production</t>
+        </is>
+      </c>
+      <c r="B139" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C139" s="23" t="inlineStr">
+        <is>
+          <t>1,000 yr7+ (4/plant) + 500 yr6 (2/plant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="23" t="inlineStr">
+        <is>
+          <t>2031+ production</t>
+        </is>
+      </c>
+      <c r="B140" s="23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>Steady state: 1,500 plants × 4 poles</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="21" t="inlineStr">
+        <is>
+          <t>LEASED LAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B143" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="23" t="inlineStr">
+        <is>
+          <t>Lease payment %</t>
+        </is>
+      </c>
+      <c r="B144" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>Of profit per leased ha (after expenses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
+          <t>Total leased ha</t>
+        </is>
+      </c>
+      <c r="B145" s="23" t="n">
         <v>60</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>Large Pool: Cost each (MXN)</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="18" t="inlineStr">
-        <is>
-          <t>Small Pools: Capacity/year</t>
-        </is>
-      </c>
-      <c r="B68" s="9">
-        <f>B61*(365/B60)*B59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="18" t="inlineStr">
-        <is>
-          <t>Large Pool: Capacity/year (each)</t>
-        </is>
-      </c>
-      <c r="B69" s="9">
-        <f>B63*(365/B64)</f>
-        <v/>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>Phase 2 expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="23" t="inlineStr">
+        <is>
+          <t>Leased start year</t>
+        </is>
+      </c>
+      <c r="B146" s="23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t>First planting</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="21" t="inlineStr">
+        <is>
+          <t>NURSERY SALES (external)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="22" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B149" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C149" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="23" t="inlineStr">
+        <is>
+          <t>Nursery sales increment/yr</t>
+        </is>
+      </c>
+      <c r="B150" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C150" s="23" t="inlineStr">
+        <is>
+          <t>Annual growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="23" t="inlineStr">
+        <is>
+          <t>Nursery sales start year</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C151" s="23" t="inlineStr">
+        <is>
+          <t>When we have surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="21" t="inlineStr">
+        <is>
+          <t>MGMT SALARY SCHEDULE (per person/month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="22" t="inlineStr">
+        <is>
+          <t>Plants per ha (existing, average)</t>
+        </is>
+      </c>
+      <c r="B153" s="22" t="n">
+        <v>150</v>
+      </c>
+      <c r="C153" s="22" t="inlineStr">
+        <is>
+          <t>1500 plants / 10 ha = 150/ha (vs 500 target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t>Bootstrap year - sweat equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="23" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B155" s="23" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t>Year 1 salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B156" s="23" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C156" s="23" t="inlineStr">
+        <is>
+          <t>Year 2 salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="23" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B157" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C157" s="23" t="inlineStr">
+        <is>
+          <t>Year 3 - reaches 30K cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="23" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B158" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K permanent</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="23" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B159" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K permanent</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="23" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B160" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C160" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends after break-even</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="23" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B161" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C161" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends from profits</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="23" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B162" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends from profits</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="23" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B163" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends from profits</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="23" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B164" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends from profits</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="23" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B165" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C165" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends from profits</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="23" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B166" s="23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>CAP: 30K — dividends from profits</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ADDITIONAL SMALL BODEGAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Bodega year 1</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Bodega year 2</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2033</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="16">
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A72:C72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1287,34 +2494,30 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Plant 2027</t>
+          <t>Plant 2027 (15ha)</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>Plant 2028</t>
+          <t>Plant 2028 (15ha)</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Plant 2029</t>
+          <t>Plant 2029 (10ha)</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Plant 2030</t>
+          <t>Plant 2030 (30ha L)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>Plant 2031</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Plant 2032</t>
-        </is>
-      </c>
+          <t>Plant 2031 (30ha L)</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="n"/>
       <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Gross Total</t>
@@ -1335,12 +2538,12 @@
       <c r="A2" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B2" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="13">
-        <f>IF(0&lt;5,0,IF(0=5,Assumptions!$B$4,IF(0=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B2" s="12">
+        <f>Assumptions!$B$135</f>
+        <v/>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D2" s="13">
         <f>IF(-1&lt;5,0,IF(-1=5,Assumptions!$B$4,IF(-1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1362,12 +2565,9 @@
         <f>IF(-5&lt;5,0,IF(-5=5,Assumptions!$B$4,IF(-5=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I2" s="13">
-        <f>IF(-6&lt;5,0,IF(-6=5,Assumptions!$B$4,IF(-6=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I2" s="13" t="n"/>
       <c r="J2" s="10">
-        <f>B2+SUM(C2:I2)</f>
+        <f>B2+SUM(C2:H2)</f>
         <v/>
       </c>
       <c r="K2" s="9">
@@ -1383,12 +2583,12 @@
       <c r="A3" s="11" t="n">
         <v>2027</v>
       </c>
-      <c r="B3" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C3" s="13">
-        <f>IF(1&lt;5,0,IF(1=5,Assumptions!$B$4,IF(1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B3" s="12">
+        <f>Assumptions!$B$136</f>
+        <v/>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D3" s="13">
         <f>IF(0&lt;5,0,IF(0=5,Assumptions!$B$4,IF(0=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1410,12 +2610,9 @@
         <f>IF(-4&lt;5,0,IF(-4=5,Assumptions!$B$4,IF(-4=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I3" s="13">
-        <f>IF(-5&lt;5,0,IF(-5=5,Assumptions!$B$4,IF(-5=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I3" s="13" t="n"/>
       <c r="J3" s="10">
-        <f>B3+SUM(C3:I3)</f>
+        <f>B3+SUM(C3:H3)</f>
         <v/>
       </c>
       <c r="K3" s="9">
@@ -1431,12 +2628,12 @@
       <c r="A4" s="11" t="n">
         <v>2028</v>
       </c>
-      <c r="B4" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C4" s="13">
-        <f>IF(2&lt;5,0,IF(2=5,Assumptions!$B$4,IF(2=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B4" s="12">
+        <f>Assumptions!$B$137</f>
+        <v/>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="13">
         <f>IF(1&lt;5,0,IF(1=5,Assumptions!$B$4,IF(1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1458,12 +2655,9 @@
         <f>IF(-3&lt;5,0,IF(-3=5,Assumptions!$B$4,IF(-3=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I4" s="13">
-        <f>IF(-4&lt;5,0,IF(-4=5,Assumptions!$B$4,IF(-4=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I4" s="13" t="n"/>
       <c r="J4" s="10">
-        <f>B4+SUM(C4:I4)</f>
+        <f>B4+SUM(C4:H4)</f>
         <v/>
       </c>
       <c r="K4" s="9">
@@ -1479,12 +2673,12 @@
       <c r="A5" s="11" t="n">
         <v>2029</v>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C5" s="13">
-        <f>IF(3&lt;5,0,IF(3=5,Assumptions!$B$4,IF(3=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B5" s="12">
+        <f>Assumptions!$B$138</f>
+        <v/>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="13">
         <f>IF(2&lt;5,0,IF(2=5,Assumptions!$B$4,IF(2=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1506,12 +2700,9 @@
         <f>IF(-2&lt;5,0,IF(-2=5,Assumptions!$B$4,IF(-2=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I5" s="13">
-        <f>IF(-3&lt;5,0,IF(-3=5,Assumptions!$B$4,IF(-3=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I5" s="13" t="n"/>
       <c r="J5" s="10">
-        <f>B5+SUM(C5:I5)</f>
+        <f>B5+SUM(C5:H5)</f>
         <v/>
       </c>
       <c r="K5" s="9">
@@ -1527,12 +2718,12 @@
       <c r="A6" s="11" t="n">
         <v>2030</v>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C6" s="13">
-        <f>IF(4&lt;5,0,IF(4=5,Assumptions!$B$4,IF(4=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B6" s="12">
+        <f>Assumptions!$B$139</f>
+        <v/>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="13">
         <f>IF(3&lt;5,0,IF(3=5,Assumptions!$B$4,IF(3=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1554,12 +2745,9 @@
         <f>IF(-1&lt;5,0,IF(-1=5,Assumptions!$B$4,IF(-1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I6" s="13">
-        <f>IF(-2&lt;5,0,IF(-2=5,Assumptions!$B$4,IF(-2=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I6" s="13" t="n"/>
       <c r="J6" s="10">
-        <f>B6+SUM(C6:I6)</f>
+        <f>B6+SUM(C6:H6)</f>
         <v/>
       </c>
       <c r="K6" s="9">
@@ -1575,12 +2763,12 @@
       <c r="A7" s="11" t="n">
         <v>2031</v>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C7" s="13">
-        <f>IF(5&lt;5,0,IF(5=5,Assumptions!$B$4,IF(5=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B7" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="13">
         <f>IF(4&lt;5,0,IF(4=5,Assumptions!$B$4,IF(4=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1602,12 +2790,9 @@
         <f>IF(0&lt;5,0,IF(0=5,Assumptions!$B$4,IF(0=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I7" s="13">
-        <f>IF(-1&lt;5,0,IF(-1=5,Assumptions!$B$4,IF(-1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I7" s="13" t="n"/>
       <c r="J7" s="10">
-        <f>B7+SUM(C7:I7)</f>
+        <f>B7+SUM(C7:H7)</f>
         <v/>
       </c>
       <c r="K7" s="9">
@@ -1623,12 +2808,12 @@
       <c r="A8" s="11" t="n">
         <v>2032</v>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C8" s="13">
-        <f>IF(6&lt;5,0,IF(6=5,Assumptions!$B$4,IF(6=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B8" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="13">
         <f>IF(5&lt;5,0,IF(5=5,Assumptions!$B$4,IF(5=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1650,12 +2835,9 @@
         <f>IF(1&lt;5,0,IF(1=5,Assumptions!$B$4,IF(1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I8" s="13">
-        <f>IF(0&lt;5,0,IF(0=5,Assumptions!$B$4,IF(0=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I8" s="13" t="n"/>
       <c r="J8" s="10">
-        <f>B8+SUM(C8:I8)</f>
+        <f>B8+SUM(C8:H8)</f>
         <v/>
       </c>
       <c r="K8" s="9">
@@ -1671,12 +2853,12 @@
       <c r="A9" s="11" t="n">
         <v>2033</v>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C9" s="13">
-        <f>IF(7&lt;5,0,IF(7=5,Assumptions!$B$4,IF(7=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B9" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="13">
         <f>IF(6&lt;5,0,IF(6=5,Assumptions!$B$4,IF(6=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1698,12 +2880,9 @@
         <f>IF(2&lt;5,0,IF(2=5,Assumptions!$B$4,IF(2=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I9" s="13">
-        <f>IF(1&lt;5,0,IF(1=5,Assumptions!$B$4,IF(1=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I9" s="13" t="n"/>
       <c r="J9" s="10">
-        <f>B9+SUM(C9:I9)</f>
+        <f>B9+SUM(C9:H9)</f>
         <v/>
       </c>
       <c r="K9" s="9">
@@ -1719,12 +2898,12 @@
       <c r="A10" s="11" t="n">
         <v>2034</v>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C10" s="13">
-        <f>IF(8&lt;5,0,IF(8=5,Assumptions!$B$4,IF(8=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B10" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="13">
         <f>IF(7&lt;5,0,IF(7=5,Assumptions!$B$4,IF(7=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1746,12 +2925,9 @@
         <f>IF(3&lt;5,0,IF(3=5,Assumptions!$B$4,IF(3=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I10" s="13">
-        <f>IF(2&lt;5,0,IF(2=5,Assumptions!$B$4,IF(2=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I10" s="13" t="n"/>
       <c r="J10" s="10">
-        <f>B10+SUM(C10:I10)</f>
+        <f>B10+SUM(C10:H10)</f>
         <v/>
       </c>
       <c r="K10" s="9">
@@ -1767,12 +2943,12 @@
       <c r="A11" s="11" t="n">
         <v>2035</v>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C11" s="13">
-        <f>IF(9&lt;5,0,IF(9=5,Assumptions!$B$4,IF(9=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B11" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D11" s="13">
         <f>IF(8&lt;5,0,IF(8=5,Assumptions!$B$4,IF(8=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1794,12 +2970,9 @@
         <f>IF(4&lt;5,0,IF(4=5,Assumptions!$B$4,IF(4=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I11" s="13">
-        <f>IF(3&lt;5,0,IF(3=5,Assumptions!$B$4,IF(3=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I11" s="13" t="n"/>
       <c r="J11" s="10">
-        <f>B11+SUM(C11:I11)</f>
+        <f>B11+SUM(C11:H11)</f>
         <v/>
       </c>
       <c r="K11" s="9">
@@ -1815,12 +2988,12 @@
       <c r="A12" s="11" t="n">
         <v>2036</v>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C12" s="13">
-        <f>IF(10&lt;5,0,IF(10=5,Assumptions!$B$4,IF(10=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B12" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="13">
         <f>IF(9&lt;5,0,IF(9=5,Assumptions!$B$4,IF(9=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1842,12 +3015,9 @@
         <f>IF(5&lt;5,0,IF(5=5,Assumptions!$B$4,IF(5=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I12" s="13">
-        <f>IF(4&lt;5,0,IF(4=5,Assumptions!$B$4,IF(4=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I12" s="13" t="n"/>
       <c r="J12" s="10">
-        <f>B12+SUM(C12:I12)</f>
+        <f>B12+SUM(C12:H12)</f>
         <v/>
       </c>
       <c r="K12" s="9">
@@ -1863,12 +3033,12 @@
       <c r="A13" s="11" t="n">
         <v>2037</v>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C13" s="13">
-        <f>IF(11&lt;5,0,IF(11=5,Assumptions!$B$4,IF(11=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B13" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D13" s="13">
         <f>IF(10&lt;5,0,IF(10=5,Assumptions!$B$4,IF(10=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1890,12 +3060,9 @@
         <f>IF(6&lt;5,0,IF(6=5,Assumptions!$B$4,IF(6=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I13" s="13">
-        <f>IF(5&lt;5,0,IF(5=5,Assumptions!$B$4,IF(5=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I13" s="13" t="n"/>
       <c r="J13" s="10">
-        <f>B13+SUM(C13:I13)</f>
+        <f>B13+SUM(C13:H13)</f>
         <v/>
       </c>
       <c r="K13" s="9">
@@ -1911,12 +3078,12 @@
       <c r="A14" s="11" t="n">
         <v>2038</v>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C14" s="13">
-        <f>IF(12&lt;5,0,IF(12=5,Assumptions!$B$4,IF(12=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$33</f>
-        <v/>
+      <c r="B14" s="12">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="13">
         <f>IF(11&lt;5,0,IF(11=5,Assumptions!$B$4,IF(11=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$34</f>
@@ -1938,12 +3105,9 @@
         <f>IF(7&lt;5,0,IF(7=5,Assumptions!$B$4,IF(7=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$38</f>
         <v/>
       </c>
-      <c r="I14" s="13">
-        <f>IF(6&lt;5,0,IF(6=5,Assumptions!$B$4,IF(6=6,Assumptions!$B$5,Assumptions!$B$6)))*Assumptions!$B$39</f>
-        <v/>
-      </c>
+      <c r="I14" s="13" t="n"/>
       <c r="J14" s="10">
-        <f>B14+SUM(C14:I14)</f>
+        <f>B14+SUM(C14:H14)</f>
         <v/>
       </c>
       <c r="K14" s="9">
@@ -1966,7 +3130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1997,7 +3161,7 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Carbon Credits (MXN)</t>
+          <t>Carbon Credits (0, external)</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -2013,6 +3177,16 @@
       <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Total Revenue (USD)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Leased Revenue</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Own Revenue</t>
         </is>
       </c>
     </row>
@@ -2042,6 +3216,14 @@
         <f>F2/Assumptions!$B$8</f>
         <v/>
       </c>
+      <c r="H2">
+        <f>(Production!G2+Production!H2)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>F2-H2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
@@ -2069,6 +3251,14 @@
         <f>F3/Assumptions!$B$8</f>
         <v/>
       </c>
+      <c r="H3">
+        <f>(Production!G3+Production!H3)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>F3-H3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -2082,9 +3272,8 @@
         <f>B4*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D4" s="9">
-        <f>Assumptions!C34*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>0</v>
@@ -2095,6 +3284,14 @@
       </c>
       <c r="G4" s="9">
         <f>F4/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>(Production!G4+Production!H4)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>F4-H4</f>
         <v/>
       </c>
     </row>
@@ -2110,9 +3307,8 @@
         <f>B5*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D5" s="9">
-        <f>Assumptions!C35*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0</v>
@@ -2123,6 +3319,14 @@
       </c>
       <c r="G5" s="9">
         <f>F5/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>(Production!G5+Production!H5)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>F5-H5</f>
         <v/>
       </c>
     </row>
@@ -2138,12 +3342,11 @@
         <f>B6*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D6" s="9">
-        <f>Assumptions!C36*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <f>5000*Assumptions!$B$17</f>
+        <f>(A6-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F6" s="10">
@@ -2152,6 +3355,14 @@
       </c>
       <c r="G6" s="9">
         <f>F6/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>(Production!G6+Production!H6)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>F6-H6</f>
         <v/>
       </c>
     </row>
@@ -2167,12 +3378,11 @@
         <f>B7*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D7" s="9">
-        <f>Assumptions!C37*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="9">
-        <f>10000*Assumptions!$B$17</f>
+        <f>(A7-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F7" s="10">
@@ -2181,6 +3391,14 @@
       </c>
       <c r="G7" s="9">
         <f>F7/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>(Production!G7+Production!H7)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>F7-H7</f>
         <v/>
       </c>
     </row>
@@ -2196,12 +3414,11 @@
         <f>B8*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D8" s="9">
-        <f>Assumptions!C38*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <f>15000*Assumptions!$B$17</f>
+        <f>(A8-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F8" s="10">
@@ -2210,6 +3427,14 @@
       </c>
       <c r="G8" s="9">
         <f>F8/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>(Production!G8+Production!H8)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>F8-H8</f>
         <v/>
       </c>
     </row>
@@ -2225,12 +3450,11 @@
         <f>B9*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D9" s="9">
-        <f>Assumptions!C39*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="9">
-        <f>20000*Assumptions!$B$17</f>
+        <f>(A9-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F9" s="10">
@@ -2239,6 +3463,14 @@
       </c>
       <c r="G9" s="9">
         <f>F9/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>(Production!G9+Production!H9)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>F9-H9</f>
         <v/>
       </c>
     </row>
@@ -2254,12 +3486,11 @@
         <f>B10*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D10" s="9">
-        <f>Assumptions!C39*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D10" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <f>25000*Assumptions!$B$17</f>
+        <f>(A10-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F10" s="10">
@@ -2268,6 +3499,14 @@
       </c>
       <c r="G10" s="9">
         <f>F10/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>(Production!G10+Production!H10)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>F10-H10</f>
         <v/>
       </c>
     </row>
@@ -2283,12 +3522,11 @@
         <f>B11*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D11" s="9">
-        <f>Assumptions!C39*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E11" s="9">
-        <f>30000*Assumptions!$B$17</f>
+        <f>(A11-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F11" s="10">
@@ -2297,6 +3535,14 @@
       </c>
       <c r="G11" s="9">
         <f>F11/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>(Production!G11+Production!H11)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>F11-H11</f>
         <v/>
       </c>
     </row>
@@ -2312,12 +3558,11 @@
         <f>B12*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D12" s="9">
-        <f>Assumptions!C39*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <f>35000*Assumptions!$B$17</f>
+        <f>(A12-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F12" s="10">
@@ -2326,6 +3571,14 @@
       </c>
       <c r="G12" s="9">
         <f>F12/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>(Production!G12+Production!H12)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>F12-H12</f>
         <v/>
       </c>
     </row>
@@ -2341,12 +3594,11 @@
         <f>B13*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D13" s="9">
-        <f>Assumptions!C39*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D13" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="9">
-        <f>40000*Assumptions!$B$17</f>
+        <f>(A13-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F13" s="10">
@@ -2355,6 +3607,14 @@
       </c>
       <c r="G13" s="9">
         <f>F13/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>(Production!G13+Production!H13)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>F13-H13</f>
         <v/>
       </c>
     </row>
@@ -2370,12 +3630,11 @@
         <f>B14*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D14" s="9">
-        <f>Assumptions!C39*Assumptions!$B$7*Assumptions!$B$8</f>
-        <v/>
+      <c r="D14" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="9">
-        <f>45000*Assumptions!$B$17</f>
+        <f>(A14-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="F14" s="10">
@@ -2384,6 +3643,14 @@
       </c>
       <c r="G14" s="9">
         <f>F14/Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>(Production!G14+Production!H14)*(1-Assumptions!$B$3)*Assumptions!$B$2</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>F14-H14</f>
         <v/>
       </c>
     </row>
@@ -2398,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2467,7 +3734,27 @@
       </c>
       <c r="K1" s="7" t="inlineStr">
         <is>
+          <t>Sub-Total (excl Lease)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Pool Liquids</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Lease Payments</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>External Clearing</t>
         </is>
       </c>
     </row>
@@ -2476,40 +3763,54 @@
         <v>2026</v>
       </c>
       <c r="B2" s="9">
-        <f>Assumptions!B33*Assumptions!$B$19*Assumptions!$B$17</f>
+        <f>3000*Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="C2" s="9">
-        <f>(2*Assumptions!$B$14+0*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C33/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D2" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^0*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A2,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E2" s="9">
-        <f>C2*0.2</f>
-        <v/>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>500000</v>
+        <f>C2*0.1</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>Assumptions!$B$108</f>
+        <v/>
       </c>
       <c r="G2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="9">
-        <f>(Assumptions!B33*0.5+Assumptions!C33*0.1)*8000</f>
-        <v/>
+      <c r="H2" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="13">
-        <f>Production!L2*5</f>
+        <f>Production!L2*Assumptions!$B$129</f>
         <v/>
       </c>
       <c r="J2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="10">
-        <f>SUM(B2:J2)</f>
+        <f>SUM(B2:J2)+L2+O2</f>
+        <v/>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>K2+M2</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>20*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2518,41 +3819,55 @@
         <v>2027</v>
       </c>
       <c r="B3" s="9">
-        <f>Assumptions!B34*Assumptions!$B$19*Assumptions!$B$17</f>
+        <f>Assumptions!B34*(Assumptions!$B$89+Assumptions!$B$19*Assumptions!$B$17)</f>
         <v/>
       </c>
       <c r="C3" s="9">
-        <f>(4*Assumptions!$B$14+1*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C34/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D3" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^1*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A3,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E3" s="9">
-        <f>C3*0.2</f>
+        <f>C3*0.1</f>
         <v/>
       </c>
       <c r="F3" s="9">
-        <f>F2*(1+Assumptions!$B$21)</f>
+        <f>Assumptions!$B$109</f>
         <v/>
       </c>
       <c r="G3" s="9" t="n">
-        <v>156000</v>
-      </c>
-      <c r="H3" s="9">
-        <f>(Assumptions!B34*0.5+Assumptions!C34*0.1)*8000</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="I3" s="13">
-        <f>Production!L3*5</f>
+        <f>Production!L3*Assumptions!$B$129</f>
         <v/>
       </c>
       <c r="J3" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="10">
-        <f>SUM(B3:J3)</f>
+        <f>SUM(B3:J3)+L3+O3</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>CEILING(Production!L3/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>K3+M3</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>Assumptions!B34*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2561,41 +3876,56 @@
         <v>2028</v>
       </c>
       <c r="B4" s="9">
-        <f>Assumptions!B35*Assumptions!$B$19*Assumptions!$B$17</f>
+        <f>Assumptions!B35*(Assumptions!$B$89+Assumptions!$B$19*Assumptions!$B$17)</f>
         <v/>
       </c>
       <c r="C4" s="9">
-        <f>(6*Assumptions!$B$14+2*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C35/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D4" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^2*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A4,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E4" s="9">
-        <f>C4*0.2</f>
+        <f>C4*0.1</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>F3*(1+Assumptions!$B$21)</f>
+        <f>Assumptions!$B$110</f>
         <v/>
       </c>
       <c r="G4" s="9" t="n">
-        <v>156000</v>
-      </c>
-      <c r="H4" s="9">
-        <f>(Assumptions!B35*0.5+Assumptions!C35*0.1)*8000</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="I4" s="13">
-        <f>Production!L4*5</f>
-        <v/>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>180000</v>
+        <f>Production!L4*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J4" s="12">
+        <f>IF(A4&gt;=Assumptions!$B$121,Assumptions!$B$120,0)</f>
+        <v/>
       </c>
       <c r="K4" s="10">
-        <f>SUM(B4:J4)</f>
+        <f>SUM(B4:J4)+L4+O4</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>CEILING(Production!L4/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>K4+M4</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>Assumptions!B35*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2604,41 +3934,57 @@
         <v>2029</v>
       </c>
       <c r="B5" s="9">
-        <f>Assumptions!B36*Assumptions!$B$19*Assumptions!$B$18</f>
+        <f>Assumptions!B36*(Assumptions!$B$89+Assumptions!$B$19*Assumptions!$B$18)</f>
         <v/>
       </c>
       <c r="C5" s="9">
-        <f>(8*Assumptions!$B$14+3*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C36/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^3*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A5,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E5" s="9">
-        <f>C5*0.2</f>
+        <f>C5*0.1</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>F4*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>156000</v>
-      </c>
-      <c r="H5" s="9">
-        <f>(Assumptions!B36*0.5+Assumptions!C36*0.1)*8000</f>
-        <v/>
+        <f>F4*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G5" s="9">
+        <f>IF(A5&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="13">
-        <f>Production!L5*5</f>
-        <v/>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>180000</v>
+        <f>Production!L5*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>IF(A5&gt;=Assumptions!$B$121,Assumptions!$B$120,0)</f>
+        <v/>
       </c>
       <c r="K5" s="10">
-        <f>SUM(B5:J5)</f>
+        <f>SUM(B5:J5)+L5+O5</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>CEILING(Production!L5/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f>K5+M5</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>Assumptions!B36*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2647,41 +3993,58 @@
         <v>2030</v>
       </c>
       <c r="B6" s="9">
-        <f>Assumptions!B37*Assumptions!$B$19*Assumptions!$B$18</f>
+        <f>Assumptions!B37*(Assumptions!$B$89+Assumptions!$B$19*Assumptions!$B$18)</f>
         <v/>
       </c>
       <c r="C6" s="9">
-        <f>(10*Assumptions!$B$14+3*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C37/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^4*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A6,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>C6*0.2</f>
+        <f>C6*0.1</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>F5*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>156000</v>
+        <f>F5*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G6" s="9">
+        <f>IF(A6&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H6" s="9">
-        <f>(Assumptions!B37*0.5+Assumptions!C37*0.1)*8000</f>
+        <f>IF(A6&gt;=Assumptions!$B$128,Assumptions!C37*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I6" s="13">
-        <f>Production!L6*5</f>
-        <v/>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>180000</v>
+        <f>Production!L6*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>IF(A6&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A6&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K6" s="10">
-        <f>SUM(B6:J6)</f>
+        <f>SUM(B6:J6)+L6+O6</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>CEILING(Production!L6/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>K6+M6</f>
+        <v/>
+      </c>
+      <c r="O6">
+        <f>Assumptions!B37*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2690,41 +4053,58 @@
         <v>2031</v>
       </c>
       <c r="B7" s="9">
-        <f>Assumptions!B38*Assumptions!$B$19*Assumptions!$B$18</f>
+        <f>Assumptions!B38*(Assumptions!$B$89+Assumptions!$B$19*Assumptions!$B$18)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>(12*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C38/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^5*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A7,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>C7*0.2</f>
+        <f>C7*0.1</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>F6*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>156000</v>
+        <f>F6*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IF(A7&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H7" s="9">
-        <f>(Assumptions!B38*0.5+Assumptions!C38*0.1)*8000</f>
+        <f>IF(A7&gt;=Assumptions!$B$128,Assumptions!C38*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>Production!L7*5</f>
-        <v/>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L7*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>IF(A7&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A7&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K7" s="10">
-        <f>SUM(B7:J7)</f>
+        <f>SUM(B7:J7)+L7+O7</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>CEILING(Production!L7/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f>K7+M7</f>
+        <v/>
+      </c>
+      <c r="O7">
+        <f>Assumptions!B38*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>
@@ -2732,43 +4112,58 @@
       <c r="A8" s="11" t="n">
         <v>2032</v>
       </c>
-      <c r="B8" s="9">
-        <f>Assumptions!B39*Assumptions!$B$19*Assumptions!$B$18</f>
-        <v/>
+      <c r="B8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C39/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^6*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A8,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>C8*0.2</f>
+        <f>C8*0.1</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>F7*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>156000</v>
+        <f>F7*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>IF(A8&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H8" s="9">
-        <f>(Assumptions!B39*0.5+Assumptions!C39*0.1)*8000</f>
+        <f>IF(A8&gt;=Assumptions!$B$128,Assumptions!C39*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>Production!L8*5</f>
-        <v/>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L8*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IF(A8&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A8&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K8" s="10">
-        <f>SUM(B8:J8)</f>
-        <v/>
+        <f>SUM(B8:J8)+L8+O8</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>CEILING(Production!L8/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f>K8+M8</f>
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2779,38 +4174,54 @@
         <v>0</v>
       </c>
       <c r="C9" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C40/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^7*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A9,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>C9*0.2</f>
+        <f>C9*0.1</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>F8*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>156000</v>
+        <f>F8*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IF(A9&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H9" s="9">
-        <f>Assumptions!C39*0.1*8000</f>
+        <f>IF(A9&gt;=Assumptions!$B$128,Assumptions!C40*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>Production!L9*5</f>
-        <v/>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L9*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>IF(A9&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A9&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K9" s="10">
-        <f>SUM(B9:J9)</f>
-        <v/>
+        <f>SUM(B9:J9)+L9+O9</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>CEILING(Production!L9/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f>K9+M9</f>
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2821,38 +4232,54 @@
         <v>0</v>
       </c>
       <c r="C10" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C40/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^8*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A10,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>C10*0.2</f>
+        <f>C10*0.1</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>F9*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>156000</v>
+        <f>F9*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G10" s="9">
+        <f>IF(A10&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H10" s="9">
-        <f>Assumptions!C39*0.1*8000</f>
+        <f>IF(A10&gt;=Assumptions!$B$128,Assumptions!C40*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>Production!L10*5</f>
-        <v/>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L10*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>IF(A10&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A10&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K10" s="10">
-        <f>SUM(B10:J10)</f>
-        <v/>
+        <f>SUM(B10:J10)+L10+O10</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>CEILING(Production!L10/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <f>K10+M10</f>
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2863,38 +4290,55 @@
         <v>0</v>
       </c>
       <c r="C11" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C40/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^9*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A11,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>C11*0.2</f>
+        <f>C11*0.1</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>F10*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>156000</v>
+        <f>F10*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>IF(A11&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H11" s="9">
-        <f>Assumptions!C39*0.1*8000</f>
+        <f>IF(A11&gt;=Assumptions!$B$128,Assumptions!C40*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>Production!L11*5</f>
-        <v/>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L11*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>IF(A11&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A11&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K11" s="10">
-        <f>SUM(B11:J11)</f>
-        <v/>
+        <f>SUM(B11:J11)+L11+O11</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>CEILING(Production!L11/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M11">
+        <f>Assumptions!$B$144*MAX(0,((Production!G11+Production!H11)*(1-Assumptions!$B$3)*Assumptions!$B$2-K11*((IF(A11-2030&gt;=5,Assumptions!$B$37,0)+IF(A11-2031&gt;=5,Assumptions!$B$38,0))/Assumptions!C40)))</f>
+        <v/>
+      </c>
+      <c r="N11">
+        <f>K11+M11</f>
+        <v/>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2905,38 +4349,55 @@
         <v>0</v>
       </c>
       <c r="C12" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C40/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^10*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A12,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>C12*0.2</f>
+        <f>C12*0.1</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>F11*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>156000</v>
+        <f>F11*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>IF(A12&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H12" s="9">
-        <f>Assumptions!C39*0.1*8000</f>
+        <f>IF(A12&gt;=Assumptions!$B$128,Assumptions!C40*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I12" s="13">
-        <f>Production!L12*5</f>
-        <v/>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L12*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J12" s="12">
+        <f>IF(A12&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A12&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K12" s="10">
-        <f>SUM(B12:J12)</f>
-        <v/>
+        <f>SUM(B12:J12)+L12+O12</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>CEILING(Production!L12/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>Assumptions!$B$144*MAX(0,((Production!G12+Production!H12)*(1-Assumptions!$B$3)*Assumptions!$B$2-K12*((IF(A12-2030&gt;=5,Assumptions!$B$37,0)+IF(A12-2031&gt;=5,Assumptions!$B$38,0))/Assumptions!C40)))</f>
+        <v/>
+      </c>
+      <c r="N12">
+        <f>K12+M12</f>
+        <v/>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2947,38 +4408,55 @@
         <v>0</v>
       </c>
       <c r="C13" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C40/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^11*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A13,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>C13*0.2</f>
+        <f>C13*0.1</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>F12*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>156000</v>
+        <f>F12*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>IF(A13&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H13" s="9">
-        <f>Assumptions!C39*0.1*8000</f>
+        <f>IF(A13&gt;=Assumptions!$B$128,Assumptions!C40*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I13" s="13">
-        <f>Production!L13*5</f>
-        <v/>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L13*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J13" s="12">
+        <f>IF(A13&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A13&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K13" s="10">
-        <f>SUM(B13:J13)</f>
-        <v/>
+        <f>SUM(B13:J13)+L13+O13</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>CEILING(Production!L13/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>Assumptions!$B$144*MAX(0,((Production!G13+Production!H13)*(1-Assumptions!$B$3)*Assumptions!$B$2-K13*((IF(A13-2030&gt;=5,Assumptions!$B$37,0)+IF(A13-2031&gt;=5,Assumptions!$B$38,0))/Assumptions!C40)))</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>K13+M13</f>
+        <v/>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2989,38 +4467,55 @@
         <v>0</v>
       </c>
       <c r="C14" s="9">
-        <f>(14*Assumptions!$B$14+4*Assumptions!$B$15)*Assumptions!$B$16*12</f>
+        <f>CEILING(Assumptions!C40/Assumptions!$B$77,1)*Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>4*Assumptions!$B$12*(1+Assumptions!$B$13)^12*12</f>
+        <f>Assumptions!$B$114*VLOOKUP(A14,Assumptions!$A$154:$B$166,2,FALSE)*12</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>C14*0.2</f>
+        <f>C14*0.1</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>F13*(1+Assumptions!$B$21)</f>
-        <v/>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>156000</v>
+        <f>F13*(1+Assumptions!$B$111)</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>IF(A14&gt;=Assumptions!$B$119,Assumptions!$B$118,0)</f>
+        <v/>
       </c>
       <c r="H14" s="9">
-        <f>Assumptions!C39*0.1*8000</f>
+        <f>IF(A14&gt;=Assumptions!$B$128,Assumptions!C40*Assumptions!$B$127,0)</f>
         <v/>
       </c>
       <c r="I14" s="13">
-        <f>Production!L14*5</f>
-        <v/>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>240000</v>
+        <f>Production!L14*Assumptions!$B$129</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>IF(A14&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A14&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <v/>
       </c>
       <c r="K14" s="10">
-        <f>SUM(B14:J14)</f>
-        <v/>
+        <f>SUM(B14:J14)+L14+O14</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>CEILING(Production!L14/Assumptions!$B$95,1)*Assumptions!$B$97</f>
+        <v/>
+      </c>
+      <c r="M14">
+        <f>Assumptions!$B$144*MAX(0,((Production!G14+Production!H14)*(1-Assumptions!$B$3)*Assumptions!$B$2-K14*((IF(A14-2030&gt;=5,Assumptions!$B$37,0)+IF(A14-2031&gt;=5,Assumptions!$B$38,0))/Assumptions!C40)))</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>K14+M14</f>
+        <v/>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3066,340 +4561,362 @@
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Fixed Items</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
         <is>
-          <t>Small Pools Built</t>
+          <t>New Pools</t>
         </is>
       </c>
       <c r="E1" s="14" t="inlineStr">
         <is>
-          <t>Large Pools Added</t>
+          <t>Bodegas</t>
         </is>
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
-          <t>Cum Large Pools</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Pool Capex (MXN)</t>
-        </is>
-      </c>
+          <t>Infra Capex</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="B2" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A2,Assumptions!B44:B55)+G2</f>
-        <v/>
-      </c>
-      <c r="D2" s="9">
-        <f>Assumptions!B61</f>
-        <v/>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="9">
-        <f>D2*Assumptions!$B$62+E2*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>C2+F2</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>SUMIF(Assumptions!C45:C57,A2,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9">
+        <f>IF(Assumptions!C33&gt;=10,1,0)</f>
+        <v/>
+      </c>
+      <c r="F2" s="9">
+        <f>E2*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
         <v>2027</v>
       </c>
       <c r="B3" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A3,Assumptions!B44:B55)+G3</f>
-        <v/>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
+        <f>C3+F3</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>SUMIF(Assumptions!C45:C57,A3,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D3" s="9">
+        <f>MAX(0,CEILING(Production!L3/Assumptions!$B$95,1)-SUM(D2:D2))</f>
+        <v/>
       </c>
       <c r="E3" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L3-Assumptions!$B$67)/Assumptions!$B$68,1)-F2)</f>
+        <f>IF(OR(A3=Assumptions!$B$170,A3=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F3" s="9">
-        <f>F2+E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="9">
-        <f>D3*Assumptions!$B$62+E3*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D3*Assumptions!$B$96+E3*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
         <v>2028</v>
       </c>
       <c r="B4" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A4,Assumptions!B44:B55)+G4</f>
-        <v/>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
+        <f>C4+F4</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>SUMIF(Assumptions!C45:C57,A4,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D4" s="9">
+        <f>MAX(0,CEILING(Production!L4/Assumptions!$B$95,1)-SUM(D2:D3))</f>
+        <v/>
       </c>
       <c r="E4" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L4-Assumptions!$B$67)/Assumptions!$B$68,1)-F3)</f>
+        <f>IF(OR(A4=Assumptions!$B$170,A4=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>F3+E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="9">
-        <f>D4*Assumptions!$B$62+E4*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D4*Assumptions!$B$96+E4*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
         <v>2029</v>
       </c>
       <c r="B5" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A5,Assumptions!B44:B55)+G5</f>
-        <v/>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
+        <f>C5+F5</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>SUMIF(Assumptions!C45:C57,A5,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D5" s="9">
+        <f>MAX(0,CEILING(Production!L5/Assumptions!$B$95,1)-SUM(D2:D4))</f>
+        <v/>
       </c>
       <c r="E5" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L5-Assumptions!$B$67)/Assumptions!$B$68,1)-F4)</f>
+        <f>IF(OR(A5=Assumptions!$B$170,A5=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>F4+E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="9">
-        <f>D5*Assumptions!$B$62+E5*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D5*Assumptions!$B$96+E5*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
         <v>2030</v>
       </c>
       <c r="B6" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A6,Assumptions!B44:B55)+G6</f>
-        <v/>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
+        <f>C6+F6</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>SUMIF(Assumptions!C45:C57,A6,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D6" s="9">
+        <f>MAX(0,CEILING(Production!L6/Assumptions!$B$95,1)-SUM(D2:D5))</f>
+        <v/>
       </c>
       <c r="E6" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L6-Assumptions!$B$67)/Assumptions!$B$68,1)-F5)</f>
+        <f>IF(OR(A6=Assumptions!$B$170,A6=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>F5+E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
-        <f>D6*Assumptions!$B$62+E6*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D6*Assumptions!$B$96+E6*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
         <v>2031</v>
       </c>
       <c r="B7" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A7,Assumptions!B44:B55)+G7</f>
-        <v/>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
+        <f>C7+F7</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUMIF(Assumptions!C45:C57,A7,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>MAX(0,CEILING(Production!L7/Assumptions!$B$95,1)-SUM(D2:D6))</f>
+        <v/>
       </c>
       <c r="E7" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L7-Assumptions!$B$67)/Assumptions!$B$68,1)-F6)</f>
+        <f>IF(OR(A7=Assumptions!$B$170,A7=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>F6+E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
-        <f>D7*Assumptions!$B$62+E7*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D7*Assumptions!$B$96+E7*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
         <v>2032</v>
       </c>
       <c r="B8" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A8,Assumptions!B44:B55)+G8</f>
-        <v/>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
+        <f>C8+F8</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>SUMIF(Assumptions!C45:C57,A8,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>MAX(0,CEILING(Production!L8/Assumptions!$B$95,1)-SUM(D2:D7))</f>
+        <v/>
       </c>
       <c r="E8" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L8-Assumptions!$B$67)/Assumptions!$B$68,1)-F7)</f>
+        <f>IF(OR(A8=Assumptions!$B$170,A8=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>F7+E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="9">
-        <f>D8*Assumptions!$B$62+E8*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D8*Assumptions!$B$96+E8*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
         <v>2033</v>
       </c>
       <c r="B9" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A9,Assumptions!B44:B55)+G9</f>
-        <v/>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0</v>
+        <f>C9+F9</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>SUMIF(Assumptions!C45:C57,A9,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D9" s="9">
+        <f>MAX(0,CEILING(Production!L9/Assumptions!$B$95,1)-SUM(D2:D8))</f>
+        <v/>
       </c>
       <c r="E9" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L9-Assumptions!$B$67)/Assumptions!$B$68,1)-F8)</f>
+        <f>IF(OR(A9=Assumptions!$B$170,A9=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>F8+E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
-        <f>D9*Assumptions!$B$62+E9*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D9*Assumptions!$B$96+E9*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
         <v>2034</v>
       </c>
       <c r="B10" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A10,Assumptions!B44:B55)+G10</f>
-        <v/>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0</v>
+        <f>C10+F10</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>SUMIF(Assumptions!C45:C57,A10,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D10" s="9">
+        <f>MAX(0,CEILING(Production!L10/Assumptions!$B$95,1)-SUM(D2:D9))</f>
+        <v/>
       </c>
       <c r="E10" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L10-Assumptions!$B$67)/Assumptions!$B$68,1)-F9)</f>
+        <f>IF(A10=Assumptions!$B$104,1,0)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>F9+E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
-        <f>D10*Assumptions!$B$62+E10*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D10*Assumptions!$B$96+E10*Assumptions!$B$103</f>
+        <v/>
+      </c>
+      <c r="G10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
         <v>2035</v>
       </c>
       <c r="B11" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A11,Assumptions!B44:B55)+G11</f>
-        <v/>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
+        <f>C11+F11</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>SUMIF(Assumptions!C45:C57,A11,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D11" s="9">
+        <f>MAX(0,CEILING(Production!L11/Assumptions!$B$95,1)-SUM(D2:D10))</f>
+        <v/>
       </c>
       <c r="E11" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L11-Assumptions!$B$67)/Assumptions!$B$68,1)-F10)</f>
+        <f>IF(OR(A11=Assumptions!$B$170,A11=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>F10+E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
-        <f>D11*Assumptions!$B$62+E11*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D11*Assumptions!$B$96+E11*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
         <v>2036</v>
       </c>
       <c r="B12" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A12,Assumptions!B44:B55)+G12</f>
-        <v/>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
+        <f>C12+F12</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>SUMIF(Assumptions!C45:C57,A12,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>MAX(0,CEILING(Production!L12/Assumptions!$B$95,1)-SUM(D2:D11))</f>
+        <v/>
       </c>
       <c r="E12" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L12-Assumptions!$B$67)/Assumptions!$B$68,1)-F11)</f>
+        <f>IF(OR(A12=Assumptions!$B$170,A12=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>F11+E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="9">
-        <f>D12*Assumptions!$B$62+E12*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D12*Assumptions!$B$96+E12*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
         <v>2037</v>
       </c>
       <c r="B13" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A13,Assumptions!B44:B55)+G13</f>
-        <v/>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
+        <f>C13+F13</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>SUMIF(Assumptions!C45:C57,A13,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D13" s="9">
+        <f>MAX(0,CEILING(Production!L13/Assumptions!$B$95,1)-SUM(D2:D12))</f>
+        <v/>
       </c>
       <c r="E13" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L13-Assumptions!$B$67)/Assumptions!$B$68,1)-F12)</f>
+        <f>IF(OR(A13=Assumptions!$B$170,A13=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>F12+E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="9">
-        <f>D13*Assumptions!$B$62+E13*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D13*Assumptions!$B$96+E13*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
         <v>2038</v>
       </c>
       <c r="B14" s="13">
-        <f>SUMIF(Assumptions!C44:C55,A14,Assumptions!B44:B55)+G14</f>
-        <v/>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
+        <f>C14+F14</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>SUMIF(Assumptions!C45:C57,A14,Assumptions!B45:B57)</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>MAX(0,CEILING(Production!L14/Assumptions!$B$95,1)-SUM(D2:D13))</f>
+        <v/>
       </c>
       <c r="E14" s="9">
-        <f>MAX(0,CEILING(MAX(0,Production!L14-Assumptions!$B$67)/Assumptions!$B$68,1)-F13)</f>
+        <f>IF(OR(A14=Assumptions!$B$170,A14=Assumptions!$B$171),1,0)</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>F13+E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="9">
-        <f>D14*Assumptions!$B$62+E14*Assumptions!$B$65</f>
-        <v/>
-      </c>
+        <f>D14*Assumptions!$B$96+E14*Assumptions!$B$102</f>
+        <v/>
+      </c>
+      <c r="G14" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3476,7 +4993,7 @@
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>Expenses!K2</f>
+        <f>Expenses!N2</f>
         <v/>
       </c>
       <c r="D2" s="13">
@@ -3509,7 +5026,7 @@
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>Expenses!K3</f>
+        <f>Expenses!N3</f>
         <v/>
       </c>
       <c r="D3" s="13">
@@ -3542,7 +5059,7 @@
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>Expenses!K4</f>
+        <f>Expenses!N4</f>
         <v/>
       </c>
       <c r="D4" s="13">
@@ -3575,7 +5092,7 @@
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>Expenses!K5</f>
+        <f>Expenses!N5</f>
         <v/>
       </c>
       <c r="D5" s="13">
@@ -3608,7 +5125,7 @@
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>Expenses!K6</f>
+        <f>Expenses!N6</f>
         <v/>
       </c>
       <c r="D6" s="13">
@@ -3641,7 +5158,7 @@
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>Expenses!K7</f>
+        <f>Expenses!N7</f>
         <v/>
       </c>
       <c r="D7" s="13">
@@ -3674,7 +5191,7 @@
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>Expenses!K8</f>
+        <f>Expenses!N8</f>
         <v/>
       </c>
       <c r="D8" s="13">
@@ -3707,7 +5224,7 @@
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>Expenses!K9</f>
+        <f>Expenses!N9</f>
         <v/>
       </c>
       <c r="D9" s="13">
@@ -3740,7 +5257,7 @@
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>Expenses!K10</f>
+        <f>Expenses!N10</f>
         <v/>
       </c>
       <c r="D10" s="13">
@@ -3773,7 +5290,7 @@
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>Expenses!K11</f>
+        <f>Expenses!N11</f>
         <v/>
       </c>
       <c r="D11" s="13">
@@ -3806,7 +5323,7 @@
         <v/>
       </c>
       <c r="C12" s="13">
-        <f>Expenses!K12</f>
+        <f>Expenses!N12</f>
         <v/>
       </c>
       <c r="D12" s="13">
@@ -3839,7 +5356,7 @@
         <v/>
       </c>
       <c r="C13" s="13">
-        <f>Expenses!K13</f>
+        <f>Expenses!N13</f>
         <v/>
       </c>
       <c r="D13" s="13">
@@ -3872,7 +5389,7 @@
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>Expenses!K14</f>
+        <f>Expenses!N14</f>
         <v/>
       </c>
       <c r="D14" s="13">
@@ -3949,36 +5466,12 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Investor Div</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Ofir Div</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Rick Div</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Juan Div</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>Diego Div</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>Total Dividends</t>
-        </is>
-      </c>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
@@ -3989,7 +5482,7 @@
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>Expenses!K2</f>
+        <f>Expenses!N2</f>
         <v/>
       </c>
       <c r="D2" s="13">
@@ -4000,30 +5493,12 @@
         <f>B2-C2-D2</f>
         <v/>
       </c>
-      <c r="F2" s="17">
-        <f>IF(AND(A2&gt;=Assumptions!$B$20,E2&gt;0),E2*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G2" s="17">
-        <f>IF(AND(A2&gt;=Assumptions!$B$20,E2&gt;0),E2*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H2" s="17">
-        <f>IF(AND(A2&gt;=Assumptions!$B$20,E2&gt;0),E2*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I2" s="17">
-        <f>IF(AND(A2&gt;=Assumptions!$B$20,E2&gt;0),E2*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J2" s="17">
-        <f>IF(AND(A2&gt;=Assumptions!$B$20,E2&gt;0),E2*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K2" s="10">
-        <f>SUM(F2:J2)</f>
-        <v/>
-      </c>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
@@ -4034,7 +5509,7 @@
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>Expenses!K3</f>
+        <f>Expenses!N3</f>
         <v/>
       </c>
       <c r="D3" s="13">
@@ -4045,30 +5520,12 @@
         <f>B3-C3-D3</f>
         <v/>
       </c>
-      <c r="F3" s="17">
-        <f>IF(AND(A3&gt;=Assumptions!$B$20,E3&gt;0),E3*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="17">
-        <f>IF(AND(A3&gt;=Assumptions!$B$20,E3&gt;0),E3*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H3" s="17">
-        <f>IF(AND(A3&gt;=Assumptions!$B$20,E3&gt;0),E3*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I3" s="17">
-        <f>IF(AND(A3&gt;=Assumptions!$B$20,E3&gt;0),E3*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J3" s="17">
-        <f>IF(AND(A3&gt;=Assumptions!$B$20,E3&gt;0),E3*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K3" s="10">
-        <f>SUM(F3:J3)</f>
-        <v/>
-      </c>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="17" t="n"/>
+      <c r="H3" s="17" t="n"/>
+      <c r="I3" s="17" t="n"/>
+      <c r="J3" s="17" t="n"/>
+      <c r="K3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -4079,7 +5536,7 @@
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>Expenses!K4</f>
+        <f>Expenses!N4</f>
         <v/>
       </c>
       <c r="D4" s="13">
@@ -4090,30 +5547,12 @@
         <f>B4-C4-D4</f>
         <v/>
       </c>
-      <c r="F4" s="17">
-        <f>IF(AND(A4&gt;=Assumptions!$B$20,E4&gt;0),E4*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="17">
-        <f>IF(AND(A4&gt;=Assumptions!$B$20,E4&gt;0),E4*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="17">
-        <f>IF(AND(A4&gt;=Assumptions!$B$20,E4&gt;0),E4*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="17">
-        <f>IF(AND(A4&gt;=Assumptions!$B$20,E4&gt;0),E4*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="17">
-        <f>IF(AND(A4&gt;=Assumptions!$B$20,E4&gt;0),E4*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="10">
-        <f>SUM(F4:J4)</f>
-        <v/>
-      </c>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -4124,7 +5563,7 @@
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>Expenses!K5</f>
+        <f>Expenses!N5</f>
         <v/>
       </c>
       <c r="D5" s="13">
@@ -4135,30 +5574,12 @@
         <f>B5-C5-D5</f>
         <v/>
       </c>
-      <c r="F5" s="17">
-        <f>IF(AND(A5&gt;=Assumptions!$B$20,E5&gt;0),E5*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="17">
-        <f>IF(AND(A5&gt;=Assumptions!$B$20,E5&gt;0),E5*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H5" s="17">
-        <f>IF(AND(A5&gt;=Assumptions!$B$20,E5&gt;0),E5*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="17">
-        <f>IF(AND(A5&gt;=Assumptions!$B$20,E5&gt;0),E5*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J5" s="17">
-        <f>IF(AND(A5&gt;=Assumptions!$B$20,E5&gt;0),E5*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K5" s="10">
-        <f>SUM(F5:J5)</f>
-        <v/>
-      </c>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -4169,7 +5590,7 @@
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>Expenses!K6</f>
+        <f>Expenses!N6</f>
         <v/>
       </c>
       <c r="D6" s="13">
@@ -4180,30 +5601,12 @@
         <f>B6-C6-D6</f>
         <v/>
       </c>
-      <c r="F6" s="17">
-        <f>IF(AND(A6&gt;=Assumptions!$B$20,E6&gt;0),E6*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="17">
-        <f>IF(AND(A6&gt;=Assumptions!$B$20,E6&gt;0),E6*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
-        <f>IF(AND(A6&gt;=Assumptions!$B$20,E6&gt;0),E6*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="17">
-        <f>IF(AND(A6&gt;=Assumptions!$B$20,E6&gt;0),E6*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="17">
-        <f>IF(AND(A6&gt;=Assumptions!$B$20,E6&gt;0),E6*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K6" s="10">
-        <f>SUM(F6:J6)</f>
-        <v/>
-      </c>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -4214,7 +5617,7 @@
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>Expenses!K7</f>
+        <f>Expenses!N7</f>
         <v/>
       </c>
       <c r="D7" s="13">
@@ -4225,30 +5628,12 @@
         <f>B7-C7-D7</f>
         <v/>
       </c>
-      <c r="F7" s="17">
-        <f>IF(AND(A7&gt;=Assumptions!$B$20,E7&gt;0),E7*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="17">
-        <f>IF(AND(A7&gt;=Assumptions!$B$20,E7&gt;0),E7*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
-        <f>IF(AND(A7&gt;=Assumptions!$B$20,E7&gt;0),E7*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="17">
-        <f>IF(AND(A7&gt;=Assumptions!$B$20,E7&gt;0),E7*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="17">
-        <f>IF(AND(A7&gt;=Assumptions!$B$20,E7&gt;0),E7*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K7" s="10">
-        <f>SUM(F7:J7)</f>
-        <v/>
-      </c>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -4259,7 +5644,7 @@
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>Expenses!K8</f>
+        <f>Expenses!N8</f>
         <v/>
       </c>
       <c r="D8" s="13">
@@ -4270,30 +5655,12 @@
         <f>B8-C8-D8</f>
         <v/>
       </c>
-      <c r="F8" s="17">
-        <f>IF(AND(A8&gt;=Assumptions!$B$20,E8&gt;0),E8*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="17">
-        <f>IF(AND(A8&gt;=Assumptions!$B$20,E8&gt;0),E8*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
-        <f>IF(AND(A8&gt;=Assumptions!$B$20,E8&gt;0),E8*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="17">
-        <f>IF(AND(A8&gt;=Assumptions!$B$20,E8&gt;0),E8*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="17">
-        <f>IF(AND(A8&gt;=Assumptions!$B$20,E8&gt;0),E8*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="10">
-        <f>SUM(F8:J8)</f>
-        <v/>
-      </c>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -4304,7 +5671,7 @@
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>Expenses!K9</f>
+        <f>Expenses!N9</f>
         <v/>
       </c>
       <c r="D9" s="13">
@@ -4315,30 +5682,12 @@
         <f>B9-C9-D9</f>
         <v/>
       </c>
-      <c r="F9" s="17">
-        <f>IF(AND(A9&gt;=Assumptions!$B$20,E9&gt;0),E9*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>IF(AND(A9&gt;=Assumptions!$B$20,E9&gt;0),E9*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>IF(AND(A9&gt;=Assumptions!$B$20,E9&gt;0),E9*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="17">
-        <f>IF(AND(A9&gt;=Assumptions!$B$20,E9&gt;0),E9*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="17">
-        <f>IF(AND(A9&gt;=Assumptions!$B$20,E9&gt;0),E9*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K9" s="10">
-        <f>SUM(F9:J9)</f>
-        <v/>
-      </c>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -4349,7 +5698,7 @@
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>Expenses!K10</f>
+        <f>Expenses!N10</f>
         <v/>
       </c>
       <c r="D10" s="13">
@@ -4360,30 +5709,12 @@
         <f>B10-C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="17">
-        <f>IF(AND(A10&gt;=Assumptions!$B$20,E10&gt;0),E10*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="17">
-        <f>IF(AND(A10&gt;=Assumptions!$B$20,E10&gt;0),E10*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
-        <f>IF(AND(A10&gt;=Assumptions!$B$20,E10&gt;0),E10*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="17">
-        <f>IF(AND(A10&gt;=Assumptions!$B$20,E10&gt;0),E10*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="17">
-        <f>IF(AND(A10&gt;=Assumptions!$B$20,E10&gt;0),E10*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="10">
-        <f>SUM(F10:J10)</f>
-        <v/>
-      </c>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -4394,7 +5725,7 @@
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>Expenses!K11</f>
+        <f>Expenses!N11</f>
         <v/>
       </c>
       <c r="D11" s="13">
@@ -4405,30 +5736,12 @@
         <f>B11-C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="17">
-        <f>IF(AND(A11&gt;=Assumptions!$B$20,E11&gt;0),E11*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="17">
-        <f>IF(AND(A11&gt;=Assumptions!$B$20,E11&gt;0),E11*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
-        <f>IF(AND(A11&gt;=Assumptions!$B$20,E11&gt;0),E11*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="17">
-        <f>IF(AND(A11&gt;=Assumptions!$B$20,E11&gt;0),E11*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="17">
-        <f>IF(AND(A11&gt;=Assumptions!$B$20,E11&gt;0),E11*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="10">
-        <f>SUM(F11:J11)</f>
-        <v/>
-      </c>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -4439,7 +5752,7 @@
         <v/>
       </c>
       <c r="C12" s="13">
-        <f>Expenses!K12</f>
+        <f>Expenses!N12</f>
         <v/>
       </c>
       <c r="D12" s="13">
@@ -4450,30 +5763,12 @@
         <f>B12-C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="17">
-        <f>IF(AND(A12&gt;=Assumptions!$B$20,E12&gt;0),E12*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="17">
-        <f>IF(AND(A12&gt;=Assumptions!$B$20,E12&gt;0),E12*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="17">
-        <f>IF(AND(A12&gt;=Assumptions!$B$20,E12&gt;0),E12*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="17">
-        <f>IF(AND(A12&gt;=Assumptions!$B$20,E12&gt;0),E12*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="17">
-        <f>IF(AND(A12&gt;=Assumptions!$B$20,E12&gt;0),E12*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K12" s="10">
-        <f>SUM(F12:J12)</f>
-        <v/>
-      </c>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -4484,7 +5779,7 @@
         <v/>
       </c>
       <c r="C13" s="13">
-        <f>Expenses!K13</f>
+        <f>Expenses!N13</f>
         <v/>
       </c>
       <c r="D13" s="13">
@@ -4495,30 +5790,12 @@
         <f>B13-C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="17">
-        <f>IF(AND(A13&gt;=Assumptions!$B$20,E13&gt;0),E13*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="17">
-        <f>IF(AND(A13&gt;=Assumptions!$B$20,E13&gt;0),E13*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>IF(AND(A13&gt;=Assumptions!$B$20,E13&gt;0),E13*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(AND(A13&gt;=Assumptions!$B$20,E13&gt;0),E13*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="17">
-        <f>IF(AND(A13&gt;=Assumptions!$B$20,E13&gt;0),E13*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K13" s="10">
-        <f>SUM(F13:J13)</f>
-        <v/>
-      </c>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -4529,7 +5806,7 @@
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>Expenses!K14</f>
+        <f>Expenses!N14</f>
         <v/>
       </c>
       <c r="D14" s="13">
@@ -4540,30 +5817,12 @@
         <f>B14-C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="17">
-        <f>IF(AND(A14&gt;=Assumptions!$B$20,E14&gt;0),E14*Assumptions!$B$23,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="17">
-        <f>IF(AND(A14&gt;=Assumptions!$B$20,E14&gt;0),E14*Assumptions!$B$24,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>IF(AND(A14&gt;=Assumptions!$B$20,E14&gt;0),E14*Assumptions!$B$25,0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(AND(A14&gt;=Assumptions!$B$20,E14&gt;0),E14*Assumptions!$B$26,0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="17">
-        <f>IF(AND(A14&gt;=Assumptions!$B$20,E14&gt;0),E14*Assumptions!$B$27,0)</f>
-        <v/>
-      </c>
-      <c r="K14" s="10">
-        <f>SUM(F14:J14)</f>
-        <v/>
-      </c>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4636,182 +5895,377 @@
       <c r="A3" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>340000</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>340000</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>340000</v>
+      <c r="B3" s="9">
+        <f>Revenue!C2*0.5+Revenue!D2+Revenue!E2</f>
+        <v/>
+      </c>
+      <c r="C3" s="9">
+        <f>Revenue!F2</f>
+        <v/>
+      </c>
+      <c r="D3" s="9">
+        <f>Revenue!C2*1.5+Revenue!D2+Revenue!E2</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>B3-Expenses!N2-Capex!B2</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>C3-Expenses!N2-Capex!B2</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>D3-Expenses!N2-Capex!B2</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
         <v>2027</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1020000</v>
+      <c r="B4" s="9">
+        <f>Revenue!C3*0.5+Revenue!D3+Revenue!E3</f>
+        <v/>
+      </c>
+      <c r="C4" s="9">
+        <f>Revenue!F3</f>
+        <v/>
+      </c>
+      <c r="D4" s="9">
+        <f>Revenue!C3*1.5+Revenue!D3+Revenue!E3</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>E3+B4-Expenses!N3-Capex!B3</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>F3+C4-Expenses!N3-Capex!B3</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>G3+D4-Expenses!N3-Capex!B3</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
         <v>2028</v>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>2040000</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>2040000</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>2040000</v>
+      <c r="B5" s="9">
+        <f>Revenue!C4*0.5+Revenue!D4+Revenue!E4</f>
+        <v/>
+      </c>
+      <c r="C5" s="9">
+        <f>Revenue!F4</f>
+        <v/>
+      </c>
+      <c r="D5" s="9">
+        <f>Revenue!C4*1.5+Revenue!D4+Revenue!E4</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>E4+B5-Expenses!N4-Capex!B4</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>F4+C5-Expenses!N4-Capex!B4</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>G4+D5-Expenses!N4-Capex!B4</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
         <v>2029</v>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>4080000</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>4080000</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>4080000</v>
+      <c r="B6" s="9">
+        <f>Revenue!C5*0.5+Revenue!D5+Revenue!E5</f>
+        <v/>
+      </c>
+      <c r="C6" s="9">
+        <f>Revenue!F5</f>
+        <v/>
+      </c>
+      <c r="D6" s="9">
+        <f>Revenue!C5*1.5+Revenue!D5+Revenue!E5</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>E5+B6-Expenses!N5-Capex!B5</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>F5+C6-Expenses!N5-Capex!B5</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>G5+D6-Expenses!N5-Capex!B5</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
         <v>2030</v>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>6120000</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>6120000</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>6120000</v>
+      <c r="B7" s="9">
+        <f>Revenue!C6*0.5+Revenue!D6+Revenue!E6</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>Revenue!F6</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>Revenue!C6*1.5+Revenue!D6+Revenue!E6</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>E6+B7-Expenses!N6-Capex!B6</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>F6+C7-Expenses!N6-Capex!B6</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>G6+D7-Expenses!N6-Capex!B6</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
         <v>2031</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>7820000</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>9520000</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>11220000</v>
+      <c r="B8" s="9">
+        <f>Revenue!C7*0.5+Revenue!D7+Revenue!E7</f>
+        <v/>
+      </c>
+      <c r="C8" s="9">
+        <f>Revenue!F7</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>Revenue!C7*1.5+Revenue!D7+Revenue!E7</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>E7+B8-Expenses!N7-Capex!B7</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>F7+C8-Expenses!N7-Capex!B7</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>G7+D8-Expenses!N7-Capex!B7</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
         <v>2032</v>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>11644800</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>17170000</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>22694800</v>
+      <c r="B9" s="9">
+        <f>Revenue!C8*0.5+Revenue!D8+Revenue!E8</f>
+        <v/>
+      </c>
+      <c r="C9" s="9">
+        <f>Revenue!F8</f>
+        <v/>
+      </c>
+      <c r="D9" s="9">
+        <f>Revenue!C8*1.5+Revenue!D8+Revenue!E8</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>E8+B9-Expenses!N8-Capex!B8</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>F8+C9-Expenses!N8-Capex!B8</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>G8+D9-Expenses!N8-Capex!B8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
         <v>2033</v>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>19294800</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>32470000</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>45644800</v>
+      <c r="B10" s="9">
+        <f>Revenue!C9*0.5+Revenue!D9+Revenue!E9</f>
+        <v/>
+      </c>
+      <c r="C10" s="9">
+        <f>Revenue!F9</f>
+        <v/>
+      </c>
+      <c r="D10" s="9">
+        <f>Revenue!C9*1.5+Revenue!D9+Revenue!E9</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>E9+B10-Expenses!N9-Capex!B9</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>F9+C10-Expenses!N9-Capex!B9</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>G9+D10-Expenses!N9-Capex!B9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
         <v>2034</v>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>28220000</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>50320000</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>72420000</v>
+      <c r="B11" s="9">
+        <f>Revenue!C10*0.5+Revenue!D10+Revenue!E10</f>
+        <v/>
+      </c>
+      <c r="C11" s="9">
+        <f>Revenue!F10</f>
+        <v/>
+      </c>
+      <c r="D11" s="9">
+        <f>Revenue!C10*1.5+Revenue!D10+Revenue!E10</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>E10+B11-Expenses!N10-Capex!B10</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>F10+C11-Expenses!N10-Capex!B10</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>G10+D11-Expenses!N10-Capex!B10</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
         <v>2035</v>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>37994800</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>69870000</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>101744800</v>
+      <c r="B12" s="9">
+        <f>Revenue!C11*0.5+Revenue!D11+Revenue!E11</f>
+        <v/>
+      </c>
+      <c r="C12" s="9">
+        <f>Revenue!F11</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>Revenue!C11*1.5+Revenue!D11+Revenue!E11</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>E11+B12-Expenses!N11-Capex!B11</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>F11+C12-Expenses!N11-Capex!B11</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>G11+D12-Expenses!N11-Capex!B11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
         <v>2036</v>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>49044800</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>91970000</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>134894800</v>
+      <c r="B13" s="9">
+        <f>Revenue!C12*0.5+Revenue!D12+Revenue!E12</f>
+        <v/>
+      </c>
+      <c r="C13" s="9">
+        <f>Revenue!F12</f>
+        <v/>
+      </c>
+      <c r="D13" s="9">
+        <f>Revenue!C12*1.5+Revenue!D12+Revenue!E12</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>E12+B13-Expenses!N12-Capex!B12</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>F12+C13-Expenses!N12-Capex!B12</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>G12+D13-Expenses!N12-Capex!B12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
         <v>2037</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>58820000</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>111520000</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>164220000</v>
+      <c r="B14" s="9">
+        <f>Revenue!C13*0.5+Revenue!D13+Revenue!E13</f>
+        <v/>
+      </c>
+      <c r="C14" s="9">
+        <f>Revenue!F13</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>Revenue!C13*1.5+Revenue!D13+Revenue!E13</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>E13+B14-Expenses!N13-Capex!B13</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>F13+C14-Expenses!N13-Capex!B13</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>G13+D14-Expenses!N13-Capex!B13</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
         <v>2038</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>65620000</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>125120000</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>184620000</v>
+      <c r="B15" s="9">
+        <f>Revenue!C14*0.5+Revenue!D14+Revenue!E14</f>
+        <v/>
+      </c>
+      <c r="C15" s="9">
+        <f>Revenue!F14</f>
+        <v/>
+      </c>
+      <c r="D15" s="9">
+        <f>Revenue!C14*1.5+Revenue!D14+Revenue!E14</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>E14+B15-Expenses!N14-Capex!B14</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>F14+C15-Expenses!N14-Capex!B14</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>G14+D15-Expenses!N14-Capex!B14</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Pacifico_Bambu_Financial_Model_v2.xlsx
+++ b/Pacifico_Bambu_Financial_Model_v2.xlsx
@@ -1971,22 +1971,22 @@
       </c>
       <c r="C133" s="23" t="inlineStr">
         <is>
-          <t>Survey: 1,500 healthy plants on 10 ha</t>
+          <t>Existing plants on 10 ha (~150/ha)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="23" t="inlineStr">
         <is>
-          <t>Target plants per ha</t>
+          <t>NEW seedlings to plant 2026 (densify)</t>
         </is>
       </c>
       <c r="B134" s="23" t="n">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>After densification</t>
+          <t>1500 existing + 3500 new = 5000 (500/ha)</t>
         </is>
       </c>
     </row>
@@ -2027,11 +2027,11 @@
         </is>
       </c>
       <c r="B137" s="23" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C137" s="23" t="inlineStr">
         <is>
-          <t>1,000 plants reach maturity (yr5)</t>
+          <t>Existing 1500 plants in yr5</t>
         </is>
       </c>
     </row>
@@ -2042,11 +2042,11 @@
         </is>
       </c>
       <c r="B138" s="23" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="C138" s="23" t="inlineStr">
         <is>
-          <t>1,000 yr6 (2/plant) + 500 yr5 (1/plant)</t>
+          <t>Steady state from 1500 existing plants</t>
         </is>
       </c>
     </row>
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="B139" s="23" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="C139" s="23" t="inlineStr">
         <is>
-          <t>1,000 yr7+ (4/plant) + 500 yr6 (2/plant)</t>
+          <t>Steady state from existing</t>
         </is>
       </c>
     </row>
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="B140" s="23" t="n">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>Steady state: 1,500 plants × 4 poles</t>
+          <t>After 2031: ALL 5000 plants mature (1500+3500)</t>
         </is>
       </c>
     </row>
@@ -2763,9 +2763,8 @@
       <c r="A7" s="11" t="n">
         <v>2031</v>
       </c>
-      <c r="B7" s="12">
-        <f>Assumptions!$B$140</f>
-        <v/>
+      <c r="B7" s="12" t="n">
+        <v>3500</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0</v>
@@ -2808,9 +2807,8 @@
       <c r="A8" s="11" t="n">
         <v>2032</v>
       </c>
-      <c r="B8" s="12">
-        <f>Assumptions!$B$140</f>
-        <v/>
+      <c r="B8" s="12" t="n">
+        <v>10500</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>0</v>
@@ -3763,7 +3761,7 @@
         <v>2026</v>
       </c>
       <c r="B2" s="9">
-        <f>3000*Assumptions!$B$18</f>
+        <f>Assumptions!$B$134*Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="C2" s="9">

--- a/Pacifico_Bambu_Financial_Model_v2.xlsx
+++ b/Pacifico_Bambu_Financial_Model_v2.xlsx
@@ -595,7 +595,12 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>500</v>
+        <v>350</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Year 5 first production (25% of mature)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -605,17 +610,27 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1000</v>
+        <v>700</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Year 6 scaling (50% of mature)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Yield yr7+ (poles/ha)</t>
+          <t>Yield yr7+ (BASE: 1,400/ha)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2000</v>
+        <v>1400</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>⚠ CONSERVATIVE BASE (range: 1,000-2,000-3,000)</t>
+        </is>
       </c>
     </row>
     <row r="7">

--- a/Pacifico_Bambu_Financial_Model_v2.xlsx
+++ b/Pacifico_Bambu_Financial_Model_v2.xlsx
@@ -246,6 +246,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Ofir</author>
+  </authors>
+  <commentList>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Pilot test: 3,000 seedlings on 6 plots × 500 seedlings. 1,500 passed 5-year R&amp;D validation.</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>Densify + expand: 3,500 new seedlings on 4 new ha → 10 ha fully planted</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -869,10 +889,10 @@
         <v>2021</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -880,7 +900,7 @@
         <v>2026</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C33" s="9">
         <f>C32+B33</f>
@@ -1986,7 +2006,7 @@
       </c>
       <c r="C133" s="23" t="inlineStr">
         <is>
-          <t>Existing plants on 10 ha (~150/ha)</t>
+          <t>Surviving plants from 6 ha pilot test (~250/ha avg)</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2021,7 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>1500 existing + 3500 new = 5000 (500/ha)</t>
+          <t>1,500 surviving + 3,500 new = 5,000 plants across 10 ha (500/ha)</t>
         </is>
       </c>
     </row>
@@ -2463,6 +2483,7 @@
     <mergeCell ref="A72:C72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3776,7 +3797,7 @@
         <v>2026</v>
       </c>
       <c r="B2" s="9">
-        <f>Assumptions!$B$134*Assumptions!$B$18</f>
+        <f>Assumptions!B33*(Assumptions!$B$89+Assumptions!$B$19*Assumptions!$B$17)</f>
         <v/>
       </c>
       <c r="C2" s="9">
@@ -3823,7 +3844,7 @@
         <v/>
       </c>
       <c r="O2">
-        <f>20*Assumptions!$B$82</f>
+        <f>Assumptions!B33*Assumptions!$B$82</f>
         <v/>
       </c>
     </row>

--- a/Pacifico_Bambu_Financial_Model_v2.xlsx
+++ b/Pacifico_Bambu_Financial_Model_v2.xlsx
@@ -662,6 +662,11 @@
       <c r="B7" s="5" t="n">
         <v>21</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Net to Pacifico after partner revenue share (~50%)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -670,7 +675,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>17</v>
+        <v>17.4103</v>
       </c>
     </row>
     <row r="9">
@@ -680,7 +685,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="10">
@@ -690,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="11">
@@ -790,7 +795,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>2030</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="21">
@@ -1879,11 +1884,11 @@
         </is>
       </c>
       <c r="B122" s="23" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="C122" s="23" t="inlineStr">
         <is>
-          <t>Verra process</t>
+          <t>Partner pays — set &gt;0 only if going in-house post-2033</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="C123" s="23" t="inlineStr">
         <is>
-          <t>After plantation matures</t>
+          <t>Optional in-house start (decision based on economics)</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3200,7 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Carbon Credits (0, external)</t>
+          <t>Carbon Credits (50% partner share)</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -3236,8 +3241,10 @@
         <f>B2*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0</v>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E2" s="9" t="n">
         <v>0</v>
@@ -3271,8 +3278,10 @@
         <f>B3*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E3" s="9" t="n">
         <v>0</v>
@@ -3306,8 +3315,9 @@
         <f>B4*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
+      <c r="D4" s="9">
+        <f>Assumptions!$C$35*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E4" s="9" t="n">
         <v>0</v>
@@ -3341,8 +3351,9 @@
         <f>B5*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
+      <c r="D5" s="9">
+        <f>Assumptions!$C$36*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E5" s="9" t="n">
         <v>0</v>
@@ -3376,8 +3387,9 @@
         <f>B6*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
+      <c r="D6" s="9">
+        <f>Assumptions!$C$37*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E6" s="9">
         <f>(A6-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3412,8 +3424,9 @@
         <f>B7*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
+      <c r="D7" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E7" s="9">
         <f>(A7-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3448,8 +3461,9 @@
         <f>B8*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
+      <c r="D8" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E8" s="9">
         <f>(A8-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3484,8 +3498,9 @@
         <f>B9*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>0</v>
+      <c r="D9" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E9" s="9">
         <f>(A9-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3520,8 +3535,9 @@
         <f>B10*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>0</v>
+      <c r="D10" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E10" s="9">
         <f>(A10-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3556,8 +3572,9 @@
         <f>B11*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
+      <c r="D11" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E11" s="9">
         <f>(A11-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3592,8 +3609,9 @@
         <f>B12*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
+      <c r="D12" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E12" s="9">
         <f>(A12-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3628,8 +3646,9 @@
         <f>B13*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
+      <c r="D13" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E13" s="9">
         <f>(A13-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>
@@ -3664,8 +3683,9 @@
         <f>B14*Assumptions!$B$2</f>
         <v/>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
+      <c r="D14" s="9">
+        <f>Assumptions!$C$38*Assumptions!$B$7*0.5*Assumptions!$B$8</f>
+        <v/>
       </c>
       <c r="E14" s="9">
         <f>(A14-Assumptions!$B$151+1)*Assumptions!$B$150*Assumptions!$B$17</f>

--- a/Pacifico_Bambu_Financial_Model_v2.xlsx
+++ b/Pacifico_Bambu_Financial_Model_v2.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C171"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -808,6 +808,7 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
@@ -865,6 +866,7 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
@@ -1247,6 +1249,7 @@
       <c r="A66" s="18" t="n"/>
       <c r="B66" s="3" t="n"/>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="18" t="n"/>
       <c r="B68" s="9" t="n"/>
@@ -1255,6 +1258,8 @@
       <c r="A69" s="18" t="n"/>
       <c r="B69" s="9" t="n"/>
     </row>
+    <row r="70"/>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="21" t="inlineStr">
         <is>
@@ -1356,6 +1361,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="21" t="inlineStr">
         <is>
@@ -1410,6 +1416,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="21" t="inlineStr">
         <is>
@@ -1480,6 +1487,7 @@
         </is>
       </c>
     </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" s="21" t="inlineStr">
         <is>
@@ -1595,6 +1603,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="21" t="inlineStr">
         <is>
@@ -1664,6 +1673,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" s="21" t="inlineStr">
         <is>
@@ -1793,6 +1803,7 @@
         </is>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
@@ -1907,6 +1918,7 @@
         </is>
       </c>
     </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" s="21" t="inlineStr">
         <is>
@@ -1976,6 +1988,7 @@
         </is>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="21" t="inlineStr">
         <is>
@@ -2120,6 +2133,7 @@
         </is>
       </c>
     </row>
+    <row r="141"/>
     <row r="142">
       <c r="A142" s="21" t="inlineStr">
         <is>
@@ -2189,6 +2203,7 @@
         </is>
       </c>
     </row>
+    <row r="147"/>
     <row r="148">
       <c r="A148" s="21" t="inlineStr">
         <is>
@@ -2434,6 +2449,7 @@
         </is>
       </c>
     </row>
+    <row r="167"/>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
@@ -2466,6 +2482,183 @@
       </c>
       <c r="B171" t="n">
         <v>2033</v>
+      </c>
+    </row>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>EXPORT PREP &amp; LOGISTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ASTM bench tests cost (one-time)</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>~$11K — Phase 1 of Pack 2, paid 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ASTM start year</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>From Round 2 earmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>FSC Chain of Custody initial</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>~$6K initial cert — paid 2031</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FSC annual maintenance</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>~$3.5K/year ongoing audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FSC start year</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>When pre-export prep deepens</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Pack 1 setup (one-time)</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SEMARNAT + Padron + APHIS + setup ~$8K</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Pack 1 setup year</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2036</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>12 months before first export</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Pack 1 per-container cost</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>~$1.5K/container — phyto + heat + broker + freight share</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Containers per year (assumed)</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Conservative 2037; scales after</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Pack 1 logistics start year</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2037</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>First export year</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3846,8 +4039,9 @@
         <f>Production!L2*Assumptions!$B$129</f>
         <v/>
       </c>
-      <c r="J2" s="12" t="n">
-        <v>0</v>
+      <c r="J2" s="12">
+        <f>IF(A2&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A2&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A2=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A2=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A2&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A2=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A2&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
+        <v/>
       </c>
       <c r="K2" s="10">
         <f>SUM(B2:J2)+L2+O2</f>
@@ -3902,8 +4096,9 @@
         <f>Production!L3*Assumptions!$B$129</f>
         <v/>
       </c>
-      <c r="J3" s="12" t="n">
-        <v>0</v>
+      <c r="J3" s="12">
+        <f>IF(A3&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A3&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A3=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A3=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A3&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A3=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A3&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
+        <v/>
       </c>
       <c r="K3" s="10">
         <f>SUM(B3:J3)+L3+O3</f>
@@ -3960,7 +4155,7 @@
         <v/>
       </c>
       <c r="J4" s="12">
-        <f>IF(A4&gt;=Assumptions!$B$121,Assumptions!$B$120,0)</f>
+        <f>IF(A4&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A4&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A4=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A4=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A4&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A4=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A4&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K4" s="10">
@@ -4019,7 +4214,7 @@
         <v/>
       </c>
       <c r="J5" s="12">
-        <f>IF(A5&gt;=Assumptions!$B$121,Assumptions!$B$120,0)</f>
+        <f>IF(A5&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A5&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A5=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A5=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A5&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A5=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A5&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K5" s="10">
@@ -4079,7 +4274,7 @@
         <v/>
       </c>
       <c r="J6" s="12">
-        <f>IF(A6&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A6&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A6&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A6&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A6=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A6=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A6&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A6=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A6&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K6" s="10">
@@ -4139,7 +4334,7 @@
         <v/>
       </c>
       <c r="J7" s="12">
-        <f>IF(A7&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A7&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A7&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A7&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A7=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A7=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A7&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A7=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A7&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K7" s="10">
@@ -4198,7 +4393,7 @@
         <v/>
       </c>
       <c r="J8" s="12">
-        <f>IF(A8&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A8&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A8&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A8&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A8=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A8=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A8&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A8=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A8&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K8" s="10">
@@ -4256,7 +4451,7 @@
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>IF(A9&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A9&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A9&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A9&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A9=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A9=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A9&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A9=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A9&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K9" s="10">
@@ -4314,7 +4509,7 @@
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IF(A10&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A10&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A10&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A10&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A10=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A10=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A10&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A10=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A10&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K10" s="10">
@@ -4372,7 +4567,7 @@
         <v/>
       </c>
       <c r="J11" s="12">
-        <f>IF(A11&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A11&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A11&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A11&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A11=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A11=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A11&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A11=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A11&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K11" s="10">
@@ -4431,7 +4626,7 @@
         <v/>
       </c>
       <c r="J12" s="12">
-        <f>IF(A12&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A12&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A12&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A12&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A12=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A12=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A12&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A12=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A12&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K12" s="10">
@@ -4490,7 +4685,7 @@
         <v/>
       </c>
       <c r="J13" s="12">
-        <f>IF(A13&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A13&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A13&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A13&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A13=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A13=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A13&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A13=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A13&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K13" s="10">
@@ -4549,7 +4744,7 @@
         <v/>
       </c>
       <c r="J14" s="12">
-        <f>IF(A14&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A14&gt;=Assumptions!$B$123,Assumptions!$B$122,0)</f>
+        <f>IF(A14&gt;=Assumptions!$B$121,Assumptions!$B$120,0)+IF(A14&gt;=Assumptions!$B$123,Assumptions!$B$122,0)+IF(A14=Assumptions!$B$178,Assumptions!$B$177,0)+IF(A14=Assumptions!$B$181,Assumptions!$B$179,0)+IF(A14&gt;Assumptions!$B$181,Assumptions!$B$180,0)+IF(A14=Assumptions!$B$183,Assumptions!$B$182,0)+IF(A14&gt;=Assumptions!$B$186,Assumptions!$B$184*Assumptions!$B$185,0)</f>
         <v/>
       </c>
       <c r="K14" s="10">
